--- a/data/raw/rba_cash_rate.xlsx
+++ b/data/raw/rba_cash_rate.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52B4BC08-35DE-4498-A8A5-B818B91DD8E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC3503FA-434C-4170-A1E5-7F1FC976BB7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1900" yWindow="1900" windowWidth="17280" windowHeight="10730" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="4" r:id="rId1"/>
@@ -236,7 +236,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -295,6 +295,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -775,22 +778,22 @@
         <v>6</v>
       </c>
       <c r="B10" s="7">
-        <v>46056</v>
+        <v>46098</v>
       </c>
       <c r="C10" s="7">
-        <v>46056</v>
+        <v>46098</v>
       </c>
       <c r="D10" s="7">
-        <v>46056</v>
+        <v>46098</v>
       </c>
       <c r="E10" s="7">
-        <v>46056</v>
+        <v>46098</v>
       </c>
       <c r="F10" s="7">
-        <v>46056</v>
+        <v>46098</v>
       </c>
       <c r="G10" s="7">
-        <v>46056</v>
+        <v>46098</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
@@ -2885,13 +2888,27 @@
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A108" s="2"/>
-      <c r="B108" s="1"/>
-      <c r="C108" s="3"/>
-      <c r="D108" s="13"/>
-      <c r="E108" s="12"/>
-      <c r="F108" s="13"/>
-      <c r="G108" s="13"/>
+      <c r="A108" s="21">
+        <v>46099</v>
+      </c>
+      <c r="B108" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="C108" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="D108" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="E108" s="12">
+        <v>4</v>
+      </c>
+      <c r="F108" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="G108" s="12">
+        <v>4.3499999999999996</v>
+      </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A109" s="2"/>
@@ -4361,7 +4378,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultColWidth="11.36328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="100.7265625" customWidth="1"/>
   </cols>

--- a/data/raw/rba_cash_rate.xlsx
+++ b/data/raw/rba_cash_rate.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC3503FA-434C-4170-A1E5-7F1FC976BB7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D140D86-8B9E-47AA-983D-44DB71C70DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="4" r:id="rId1"/>
@@ -165,7 +165,7 @@
     <numFmt numFmtId="164" formatCode="[&lt;0]\-0.00;[&gt;0]\+0.00;General"/>
     <numFmt numFmtId="165" formatCode="dd\-mmm\-yyyy"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -200,13 +200,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="9"/>
       <color theme="1"/>
@@ -236,7 +229,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -274,9 +267,6 @@
     <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -293,7 +283,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -606,18 +596,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C9F740B-1B11-4070-841A-838BC6048348}">
   <dimension ref="A1:G271"/>
-  <sheetFormatPr defaultColWidth="30.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="30.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.26953125" customWidth="1"/>
-    <col min="2" max="7" width="28.81640625" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" customWidth="1"/>
+    <col min="2" max="7" width="28.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="18" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="20" t="s">
+    <row r="1" spans="1:7" s="17" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="19" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -640,11 +630,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:7" s="18" customFormat="1" ht="35.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" s="17" customFormat="1" ht="35.4" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="18" t="s">
         <v>17</v>
       </c>
       <c r="C3" s="4" t="s">
@@ -663,7 +653,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
@@ -686,7 +676,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>3</v>
       </c>
@@ -709,7 +699,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
@@ -732,7 +722,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -741,7 +731,7 @@
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -750,7 +740,7 @@
       <c r="F8" s="8"/>
       <c r="G8" s="8"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>5</v>
       </c>
@@ -773,30 +763,30 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>6</v>
       </c>
       <c r="B10" s="7">
-        <v>46098</v>
+        <v>46147</v>
       </c>
       <c r="C10" s="7">
-        <v>46098</v>
+        <v>46147</v>
       </c>
       <c r="D10" s="7">
-        <v>46098</v>
+        <v>46147</v>
       </c>
       <c r="E10" s="7">
-        <v>46098</v>
+        <v>46147</v>
       </c>
       <c r="F10" s="7">
-        <v>46098</v>
+        <v>46147</v>
       </c>
       <c r="G10" s="7">
-        <v>46098</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+        <v>46147</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>7</v>
       </c>
@@ -819,7 +809,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>32896</v>
       </c>
@@ -834,7 +824,7 @@
       <c r="F12" s="1"/>
       <c r="G12" s="12"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>32919</v>
       </c>
@@ -849,7 +839,7 @@
       <c r="F13" s="1"/>
       <c r="G13" s="12"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>32967</v>
       </c>
@@ -864,7 +854,7 @@
       <c r="F14" s="1"/>
       <c r="G14" s="12"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>33087</v>
       </c>
@@ -879,7 +869,7 @@
       <c r="F15" s="1"/>
       <c r="G15" s="12"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>33161</v>
       </c>
@@ -894,7 +884,7 @@
       <c r="F16" s="1"/>
       <c r="G16" s="12"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>33225</v>
       </c>
@@ -909,7 +899,7 @@
       <c r="F17" s="1"/>
       <c r="G17" s="12"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>33332</v>
       </c>
@@ -924,7 +914,7 @@
       <c r="F18" s="1"/>
       <c r="G18" s="12"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>33374</v>
       </c>
@@ -939,7 +929,7 @@
       <c r="F19" s="1"/>
       <c r="G19" s="12"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>33484</v>
       </c>
@@ -954,7 +944,7 @@
       <c r="F20" s="1"/>
       <c r="G20" s="12"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>33548</v>
       </c>
@@ -969,7 +959,7 @@
       <c r="F21" s="1"/>
       <c r="G21" s="12"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>33611</v>
       </c>
@@ -984,7 +974,7 @@
       <c r="F22" s="1"/>
       <c r="G22" s="12"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>33730</v>
       </c>
@@ -999,7 +989,7 @@
       <c r="F23" s="1"/>
       <c r="G23" s="12"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>33793</v>
       </c>
@@ -1014,7 +1004,7 @@
       <c r="F24" s="1"/>
       <c r="G24" s="12"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>34051</v>
       </c>
@@ -1029,7 +1019,7 @@
       <c r="F25" s="1"/>
       <c r="G25" s="12"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>34180</v>
       </c>
@@ -1044,7 +1034,7 @@
       <c r="F26" s="1"/>
       <c r="G26" s="12"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>34563</v>
       </c>
@@ -1059,7 +1049,7 @@
       <c r="F27" s="1"/>
       <c r="G27" s="12"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>34631</v>
       </c>
@@ -1074,7 +1064,7 @@
       <c r="F28" s="1"/>
       <c r="G28" s="12"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
         <v>34682</v>
       </c>
@@ -1093,7 +1083,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
         <v>35277</v>
       </c>
@@ -1116,7 +1106,7 @@
         <v>7.25</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
         <v>35375</v>
       </c>
@@ -1139,7 +1129,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
         <v>35410</v>
       </c>
@@ -1162,7 +1152,7 @@
         <v>6.25</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
         <v>35573</v>
       </c>
@@ -1185,7 +1175,7 @@
         <v>5.75</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
         <v>35641</v>
       </c>
@@ -1208,8 +1198,8 @@
         <v>5.25</v>
       </c>
     </row>
-    <row r="35" spans="1:7" s="17" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="15">
+    <row r="35" spans="1:7" s="16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="14">
         <v>35704</v>
       </c>
       <c r="B35" s="1">
@@ -1221,17 +1211,17 @@
       <c r="D35" s="1">
         <v>-0.15000000000000036</v>
       </c>
-      <c r="E35" s="16">
+      <c r="E35" s="15">
         <v>4.75</v>
       </c>
       <c r="F35" s="1">
         <v>0</v>
       </c>
-      <c r="G35" s="16">
+      <c r="G35" s="15">
         <v>5.25</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
         <v>36131</v>
       </c>
@@ -1254,7 +1244,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
         <v>36467</v>
       </c>
@@ -1277,7 +1267,7 @@
         <v>5.25</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
         <v>36558</v>
       </c>
@@ -1300,7 +1290,7 @@
         <v>5.75</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
         <v>36621</v>
       </c>
@@ -1323,7 +1313,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
         <v>36649</v>
       </c>
@@ -1346,7 +1336,7 @@
         <v>6.25</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
         <v>36740</v>
       </c>
@@ -1369,7 +1359,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
         <v>36929</v>
       </c>
@@ -1392,7 +1382,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
         <v>36957</v>
       </c>
@@ -1415,7 +1405,7 @@
         <v>5.75</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
         <v>36985</v>
       </c>
@@ -1438,7 +1428,7 @@
         <v>5.25</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="2">
         <v>37139</v>
       </c>
@@ -1461,7 +1451,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="2">
         <v>37167</v>
       </c>
@@ -1484,7 +1474,7 @@
         <v>4.75</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="2">
         <v>37230</v>
       </c>
@@ -1507,7 +1497,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="2">
         <v>37384</v>
       </c>
@@ -1530,7 +1520,7 @@
         <v>4.75</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="2">
         <v>37412</v>
       </c>
@@ -1553,7 +1543,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="2">
         <v>37930</v>
       </c>
@@ -1576,7 +1566,7 @@
         <v>5.25</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" s="2">
         <v>37958</v>
       </c>
@@ -1599,7 +1589,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="2">
         <v>38413</v>
       </c>
@@ -1622,7 +1612,7 @@
         <v>5.75</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="2">
         <v>38840</v>
       </c>
@@ -1645,7 +1635,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="2">
         <v>38931</v>
       </c>
@@ -1668,7 +1658,7 @@
         <v>6.25</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" s="2">
         <v>39029</v>
       </c>
@@ -1691,7 +1681,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" s="2">
         <v>39302</v>
       </c>
@@ -1714,7 +1704,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="2">
         <v>39393</v>
       </c>
@@ -1737,7 +1727,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" s="2">
         <v>39484</v>
       </c>
@@ -1760,7 +1750,7 @@
         <v>7.25</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" s="2">
         <v>39512</v>
       </c>
@@ -1783,7 +1773,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" s="2">
         <v>39694</v>
       </c>
@@ -1806,7 +1796,7 @@
         <v>7.25</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" s="2">
         <v>39729</v>
       </c>
@@ -1829,7 +1819,7 @@
         <v>6.25</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" s="2">
         <v>39757</v>
       </c>
@@ -1852,7 +1842,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" s="2">
         <v>39785</v>
       </c>
@@ -1875,7 +1865,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" s="2">
         <v>39848</v>
       </c>
@@ -1898,7 +1888,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" s="2">
         <v>39911</v>
       </c>
@@ -1921,7 +1911,7 @@
         <v>3.25</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" s="2">
         <v>40093</v>
       </c>
@@ -1944,7 +1934,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" s="2">
         <v>40121</v>
       </c>
@@ -1967,7 +1957,7 @@
         <v>3.75</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" s="2">
         <v>40149</v>
       </c>
@@ -1990,7 +1980,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" s="2">
         <v>40240</v>
       </c>
@@ -2013,7 +2003,7 @@
         <v>4.25</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" s="2">
         <v>40275</v>
       </c>
@@ -2036,7 +2026,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" s="2">
         <v>40303</v>
       </c>
@@ -2059,7 +2049,7 @@
         <v>4.75</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" s="2">
         <v>40485</v>
       </c>
@@ -2082,7 +2072,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" s="2">
         <v>40849</v>
       </c>
@@ -2105,7 +2095,7 @@
         <v>4.75</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" s="2">
         <v>40884</v>
       </c>
@@ -2128,7 +2118,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" s="2">
         <v>41031</v>
       </c>
@@ -2151,7 +2141,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" s="2">
         <v>41066</v>
       </c>
@@ -2174,7 +2164,7 @@
         <v>3.75</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" s="2">
         <v>41185</v>
       </c>
@@ -2197,7 +2187,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" s="2">
         <v>41248</v>
       </c>
@@ -2220,7 +2210,7 @@
         <v>3.25</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" s="2">
         <v>41402</v>
       </c>
@@ -2243,7 +2233,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" s="2">
         <v>41493</v>
       </c>
@@ -2266,7 +2256,7 @@
         <v>2.75</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" s="2">
         <v>42039</v>
       </c>
@@ -2289,7 +2279,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" s="2">
         <v>42130</v>
       </c>
@@ -2312,7 +2302,7 @@
         <v>2.25</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" s="2">
         <v>42494</v>
       </c>
@@ -2335,7 +2325,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" s="2">
         <v>42585</v>
       </c>
@@ -2358,7 +2348,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" s="2">
         <v>43621</v>
       </c>
@@ -2381,7 +2371,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" s="2">
         <v>43649</v>
       </c>
@@ -2404,7 +2394,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" s="2">
         <v>43740</v>
       </c>
@@ -2427,7 +2417,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" s="2">
         <v>43894</v>
       </c>
@@ -2450,7 +2440,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" s="2">
         <v>43910</v>
       </c>
@@ -2473,7 +2463,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" s="2">
         <v>44139</v>
       </c>
@@ -2496,7 +2486,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" s="2">
         <v>44685</v>
       </c>
@@ -2519,7 +2509,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" s="2">
         <v>44720</v>
       </c>
@@ -2542,7 +2532,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" s="2">
         <v>44748</v>
       </c>
@@ -2565,7 +2555,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" s="2">
         <v>44776</v>
       </c>
@@ -2588,7 +2578,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" s="2">
         <v>44811</v>
       </c>
@@ -2611,7 +2601,7 @@
         <v>2.6</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" s="2">
         <v>44839</v>
       </c>
@@ -2634,7 +2624,7 @@
         <v>2.85</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" s="2">
         <v>44867</v>
       </c>
@@ -2657,7 +2647,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" s="2">
         <v>44902</v>
       </c>
@@ -2680,7 +2670,7 @@
         <v>3.35</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" s="2">
         <v>44965</v>
       </c>
@@ -2703,7 +2693,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" s="2">
         <v>44993</v>
       </c>
@@ -2726,7 +2716,7 @@
         <v>3.85</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" s="2">
         <v>45049</v>
       </c>
@@ -2749,7 +2739,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" s="2">
         <v>45084</v>
       </c>
@@ -2772,7 +2762,7 @@
         <v>4.3499999999999996</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" s="2">
         <v>45238</v>
       </c>
@@ -2795,7 +2785,7 @@
         <v>4.5999999999999996</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" s="2">
         <v>45707</v>
       </c>
@@ -2818,7 +2808,7 @@
         <v>4.3499999999999996</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105" s="2">
         <v>45798</v>
       </c>
@@ -2841,7 +2831,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106" s="2">
         <v>45882</v>
       </c>
@@ -2864,7 +2854,7 @@
         <v>3.85</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" s="2">
         <v>46057</v>
       </c>
@@ -2887,8 +2877,8 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A108" s="21">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A108" s="20">
         <v>46099</v>
       </c>
       <c r="B108" s="1">
@@ -2910,1464 +2900,1478 @@
         <v>4.3499999999999996</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A109" s="2"/>
-      <c r="B109" s="1"/>
-      <c r="C109" s="3"/>
-      <c r="D109" s="13"/>
-      <c r="E109" s="12"/>
-      <c r="F109" s="13"/>
-      <c r="G109" s="13"/>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A109" s="2">
+        <v>46148</v>
+      </c>
+      <c r="B109" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="C109" s="3">
+        <v>4.3499999999999996</v>
+      </c>
+      <c r="D109" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="E109" s="12">
+        <v>4.25</v>
+      </c>
+      <c r="F109" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="G109" s="12">
+        <v>4.5999999999999996</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110" s="2"/>
       <c r="B110" s="1"/>
       <c r="C110" s="3"/>
-      <c r="D110" s="14"/>
+      <c r="D110" s="13"/>
       <c r="E110" s="12"/>
-      <c r="F110" s="14"/>
-      <c r="G110" s="14"/>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F110" s="13"/>
+      <c r="G110" s="13"/>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111" s="2"/>
       <c r="B111" s="1"/>
       <c r="C111" s="3"/>
-      <c r="D111" s="14"/>
+      <c r="D111" s="13"/>
       <c r="E111" s="12"/>
-      <c r="F111" s="14"/>
-      <c r="G111" s="14"/>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F111" s="13"/>
+      <c r="G111" s="13"/>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112" s="2"/>
       <c r="B112" s="1"/>
       <c r="C112" s="3"/>
-      <c r="D112" s="14"/>
+      <c r="D112" s="13"/>
       <c r="E112" s="12"/>
-      <c r="F112" s="14"/>
-      <c r="G112" s="14"/>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F112" s="13"/>
+      <c r="G112" s="13"/>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" s="2"/>
       <c r="B113" s="3"/>
       <c r="C113" s="3"/>
-      <c r="D113" s="14"/>
+      <c r="D113" s="13"/>
       <c r="E113" s="12"/>
-      <c r="F113" s="14"/>
-      <c r="G113" s="14"/>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F113" s="13"/>
+      <c r="G113" s="13"/>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" s="2"/>
       <c r="B114" s="3"/>
       <c r="C114" s="3"/>
-      <c r="D114" s="14"/>
+      <c r="D114" s="13"/>
       <c r="E114" s="12"/>
-      <c r="F114" s="14"/>
-      <c r="G114" s="14"/>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F114" s="13"/>
+      <c r="G114" s="13"/>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115" s="2"/>
       <c r="B115" s="3"/>
       <c r="C115" s="3"/>
-      <c r="D115" s="14"/>
+      <c r="D115" s="13"/>
       <c r="E115" s="12"/>
-      <c r="F115" s="14"/>
-      <c r="G115" s="14"/>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F115" s="13"/>
+      <c r="G115" s="13"/>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" s="2"/>
       <c r="B116" s="3"/>
       <c r="C116" s="3"/>
-      <c r="D116" s="14"/>
+      <c r="D116" s="13"/>
       <c r="E116" s="12"/>
-      <c r="F116" s="14"/>
-      <c r="G116" s="14"/>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F116" s="13"/>
+      <c r="G116" s="13"/>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117" s="2"/>
       <c r="B117" s="3"/>
       <c r="C117" s="3"/>
-      <c r="D117" s="14"/>
+      <c r="D117" s="13"/>
       <c r="E117" s="12"/>
-      <c r="F117" s="14"/>
-      <c r="G117" s="14"/>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F117" s="13"/>
+      <c r="G117" s="13"/>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118" s="2"/>
       <c r="B118" s="3"/>
       <c r="C118" s="3"/>
-      <c r="D118" s="14"/>
+      <c r="D118" s="13"/>
       <c r="E118" s="12"/>
-      <c r="F118" s="14"/>
-      <c r="G118" s="14"/>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F118" s="13"/>
+      <c r="G118" s="13"/>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119" s="2"/>
       <c r="B119" s="3"/>
       <c r="C119" s="3"/>
-      <c r="D119" s="14"/>
+      <c r="D119" s="13"/>
       <c r="E119" s="12"/>
-      <c r="F119" s="14"/>
-      <c r="G119" s="14"/>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F119" s="13"/>
+      <c r="G119" s="13"/>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120" s="2"/>
       <c r="B120" s="3"/>
       <c r="C120" s="3"/>
-      <c r="D120" s="14"/>
+      <c r="D120" s="13"/>
       <c r="E120" s="12"/>
-      <c r="F120" s="14"/>
-      <c r="G120" s="14"/>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F120" s="13"/>
+      <c r="G120" s="13"/>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121" s="2"/>
       <c r="B121" s="3"/>
       <c r="C121" s="3"/>
-      <c r="D121" s="14"/>
+      <c r="D121" s="13"/>
       <c r="E121" s="12"/>
-      <c r="F121" s="14"/>
-      <c r="G121" s="14"/>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F121" s="13"/>
+      <c r="G121" s="13"/>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122" s="2"/>
       <c r="B122" s="3"/>
       <c r="C122" s="3"/>
-      <c r="D122" s="14"/>
+      <c r="D122" s="13"/>
       <c r="E122" s="12"/>
-      <c r="F122" s="14"/>
-      <c r="G122" s="14"/>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F122" s="13"/>
+      <c r="G122" s="13"/>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123" s="2"/>
       <c r="B123" s="3"/>
       <c r="C123" s="3"/>
-      <c r="D123" s="14"/>
+      <c r="D123" s="13"/>
       <c r="E123" s="12"/>
-      <c r="F123" s="14"/>
-      <c r="G123" s="14"/>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F123" s="13"/>
+      <c r="G123" s="13"/>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124" s="2"/>
       <c r="B124" s="3"/>
       <c r="C124" s="3"/>
-      <c r="D124" s="14"/>
+      <c r="D124" s="13"/>
       <c r="E124" s="12"/>
-      <c r="F124" s="14"/>
-      <c r="G124" s="14"/>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F124" s="13"/>
+      <c r="G124" s="13"/>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A125" s="2"/>
       <c r="B125" s="3"/>
       <c r="C125" s="3"/>
-      <c r="D125" s="14"/>
+      <c r="D125" s="13"/>
       <c r="E125" s="12"/>
-      <c r="F125" s="14"/>
-      <c r="G125" s="14"/>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F125" s="13"/>
+      <c r="G125" s="13"/>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126" s="2"/>
       <c r="B126" s="3"/>
       <c r="C126" s="3"/>
-      <c r="D126" s="14"/>
+      <c r="D126" s="13"/>
       <c r="E126" s="12"/>
-      <c r="F126" s="14"/>
-      <c r="G126" s="14"/>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F126" s="13"/>
+      <c r="G126" s="13"/>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127" s="2"/>
       <c r="B127" s="3"/>
       <c r="C127" s="3"/>
-      <c r="D127" s="14"/>
+      <c r="D127" s="13"/>
       <c r="E127" s="12"/>
-      <c r="F127" s="14"/>
-      <c r="G127" s="14"/>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F127" s="13"/>
+      <c r="G127" s="13"/>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A128" s="2"/>
       <c r="B128" s="3"/>
       <c r="C128" s="3"/>
-      <c r="D128" s="14"/>
+      <c r="D128" s="13"/>
       <c r="E128" s="12"/>
-      <c r="F128" s="14"/>
-      <c r="G128" s="14"/>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F128" s="13"/>
+      <c r="G128" s="13"/>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A129" s="2"/>
       <c r="B129" s="3"/>
       <c r="C129" s="3"/>
-      <c r="D129" s="14"/>
+      <c r="D129" s="13"/>
       <c r="E129" s="12"/>
-      <c r="F129" s="14"/>
-      <c r="G129" s="14"/>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F129" s="13"/>
+      <c r="G129" s="13"/>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A130" s="2"/>
       <c r="B130" s="3"/>
       <c r="C130" s="3"/>
-      <c r="D130" s="14"/>
+      <c r="D130" s="13"/>
       <c r="E130" s="12"/>
-      <c r="F130" s="14"/>
-      <c r="G130" s="14"/>
-    </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F130" s="13"/>
+      <c r="G130" s="13"/>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A131" s="2"/>
       <c r="B131" s="3"/>
       <c r="C131" s="3"/>
-      <c r="D131" s="14"/>
+      <c r="D131" s="13"/>
       <c r="E131" s="12"/>
-      <c r="F131" s="14"/>
-      <c r="G131" s="14"/>
-    </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F131" s="13"/>
+      <c r="G131" s="13"/>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A132" s="2"/>
       <c r="B132" s="3"/>
       <c r="C132" s="3"/>
-      <c r="D132" s="14"/>
+      <c r="D132" s="13"/>
       <c r="E132" s="12"/>
-      <c r="F132" s="14"/>
-      <c r="G132" s="14"/>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F132" s="13"/>
+      <c r="G132" s="13"/>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A133" s="2"/>
       <c r="B133" s="3"/>
       <c r="C133" s="3"/>
-      <c r="D133" s="14"/>
+      <c r="D133" s="13"/>
       <c r="E133" s="12"/>
-      <c r="F133" s="14"/>
-      <c r="G133" s="14"/>
-    </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F133" s="13"/>
+      <c r="G133" s="13"/>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A134" s="2"/>
       <c r="B134" s="3"/>
       <c r="C134" s="3"/>
-      <c r="D134" s="14"/>
+      <c r="D134" s="13"/>
       <c r="E134" s="12"/>
-      <c r="F134" s="14"/>
-      <c r="G134" s="14"/>
-    </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F134" s="13"/>
+      <c r="G134" s="13"/>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A135" s="2"/>
       <c r="B135" s="3"/>
       <c r="C135" s="3"/>
-      <c r="D135" s="14"/>
+      <c r="D135" s="13"/>
       <c r="E135" s="12"/>
-      <c r="F135" s="14"/>
-      <c r="G135" s="14"/>
-    </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F135" s="13"/>
+      <c r="G135" s="13"/>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A136" s="2"/>
       <c r="B136" s="3"/>
       <c r="C136" s="3"/>
-      <c r="D136" s="14"/>
+      <c r="D136" s="13"/>
       <c r="E136" s="12"/>
-      <c r="F136" s="14"/>
-      <c r="G136" s="14"/>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F136" s="13"/>
+      <c r="G136" s="13"/>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A137" s="2"/>
       <c r="B137" s="3"/>
       <c r="C137" s="3"/>
-      <c r="D137" s="14"/>
+      <c r="D137" s="13"/>
       <c r="E137" s="12"/>
-      <c r="F137" s="14"/>
-      <c r="G137" s="14"/>
-    </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F137" s="13"/>
+      <c r="G137" s="13"/>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A138" s="2"/>
       <c r="B138" s="3"/>
       <c r="C138" s="3"/>
-      <c r="D138" s="14"/>
+      <c r="D138" s="13"/>
       <c r="E138" s="12"/>
-      <c r="F138" s="14"/>
-      <c r="G138" s="14"/>
-    </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F138" s="13"/>
+      <c r="G138" s="13"/>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A139" s="2"/>
       <c r="B139" s="3"/>
       <c r="C139" s="3"/>
-      <c r="D139" s="14"/>
+      <c r="D139" s="13"/>
       <c r="E139" s="12"/>
-      <c r="F139" s="14"/>
-      <c r="G139" s="14"/>
-    </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F139" s="13"/>
+      <c r="G139" s="13"/>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A140" s="2"/>
       <c r="B140" s="3"/>
       <c r="C140" s="3"/>
-      <c r="D140" s="14"/>
+      <c r="D140" s="13"/>
       <c r="E140" s="12"/>
-      <c r="F140" s="14"/>
-      <c r="G140" s="14"/>
-    </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F140" s="13"/>
+      <c r="G140" s="13"/>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A141" s="2"/>
       <c r="B141" s="3"/>
       <c r="C141" s="3"/>
-      <c r="D141" s="14"/>
+      <c r="D141" s="13"/>
       <c r="E141" s="12"/>
-      <c r="F141" s="14"/>
-      <c r="G141" s="14"/>
-    </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F141" s="13"/>
+      <c r="G141" s="13"/>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A142" s="2"/>
       <c r="B142" s="3"/>
       <c r="C142" s="3"/>
-      <c r="D142" s="14"/>
+      <c r="D142" s="13"/>
       <c r="E142" s="12"/>
-      <c r="F142" s="14"/>
-      <c r="G142" s="14"/>
-    </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F142" s="13"/>
+      <c r="G142" s="13"/>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A143" s="2"/>
       <c r="B143" s="3"/>
       <c r="C143" s="3"/>
-      <c r="D143" s="14"/>
+      <c r="D143" s="13"/>
       <c r="E143" s="12"/>
-      <c r="F143" s="14"/>
-      <c r="G143" s="14"/>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F143" s="13"/>
+      <c r="G143" s="13"/>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A144" s="2"/>
       <c r="B144" s="3"/>
       <c r="C144" s="3"/>
-      <c r="D144" s="14"/>
+      <c r="D144" s="13"/>
       <c r="E144" s="12"/>
-      <c r="F144" s="14"/>
-      <c r="G144" s="14"/>
-    </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F144" s="13"/>
+      <c r="G144" s="13"/>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A145" s="2"/>
       <c r="B145" s="3"/>
       <c r="C145" s="3"/>
-      <c r="D145" s="14"/>
+      <c r="D145" s="13"/>
       <c r="E145" s="12"/>
-      <c r="F145" s="14"/>
-      <c r="G145" s="14"/>
-    </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F145" s="13"/>
+      <c r="G145" s="13"/>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A146" s="2"/>
       <c r="B146" s="3"/>
       <c r="C146" s="3"/>
-      <c r="D146" s="14"/>
+      <c r="D146" s="13"/>
       <c r="E146" s="12"/>
-      <c r="F146" s="14"/>
-      <c r="G146" s="14"/>
-    </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F146" s="13"/>
+      <c r="G146" s="13"/>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A147" s="2"/>
       <c r="B147" s="3"/>
       <c r="C147" s="3"/>
-      <c r="D147" s="14"/>
+      <c r="D147" s="13"/>
       <c r="E147" s="12"/>
-      <c r="F147" s="14"/>
-      <c r="G147" s="14"/>
-    </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F147" s="13"/>
+      <c r="G147" s="13"/>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A148" s="2"/>
       <c r="B148" s="3"/>
       <c r="C148" s="3"/>
-      <c r="D148" s="14"/>
+      <c r="D148" s="13"/>
       <c r="E148" s="12"/>
-      <c r="F148" s="14"/>
-      <c r="G148" s="14"/>
-    </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F148" s="13"/>
+      <c r="G148" s="13"/>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A149" s="2"/>
       <c r="B149" s="3"/>
       <c r="C149" s="3"/>
-      <c r="D149" s="14"/>
+      <c r="D149" s="13"/>
       <c r="E149" s="12"/>
-      <c r="F149" s="14"/>
-      <c r="G149" s="14"/>
-    </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F149" s="13"/>
+      <c r="G149" s="13"/>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A150" s="2"/>
       <c r="B150" s="3"/>
       <c r="C150" s="3"/>
-      <c r="D150" s="14"/>
+      <c r="D150" s="13"/>
       <c r="E150" s="12"/>
-      <c r="F150" s="14"/>
-      <c r="G150" s="14"/>
-    </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F150" s="13"/>
+      <c r="G150" s="13"/>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A151" s="2"/>
       <c r="B151" s="3"/>
       <c r="C151" s="3"/>
-      <c r="D151" s="14"/>
+      <c r="D151" s="13"/>
       <c r="E151" s="12"/>
-      <c r="F151" s="14"/>
-      <c r="G151" s="14"/>
-    </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F151" s="13"/>
+      <c r="G151" s="13"/>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A152" s="2"/>
       <c r="B152" s="3"/>
       <c r="C152" s="3"/>
-      <c r="D152" s="14"/>
+      <c r="D152" s="13"/>
       <c r="E152" s="12"/>
-      <c r="F152" s="14"/>
-      <c r="G152" s="14"/>
-    </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F152" s="13"/>
+      <c r="G152" s="13"/>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A153" s="2"/>
       <c r="B153" s="3"/>
       <c r="C153" s="3"/>
-      <c r="D153" s="14"/>
+      <c r="D153" s="13"/>
       <c r="E153" s="12"/>
-      <c r="F153" s="14"/>
-      <c r="G153" s="14"/>
-    </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F153" s="13"/>
+      <c r="G153" s="13"/>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A154" s="2"/>
       <c r="B154" s="3"/>
       <c r="C154" s="3"/>
-      <c r="D154" s="14"/>
+      <c r="D154" s="13"/>
       <c r="E154" s="12"/>
-      <c r="F154" s="14"/>
-      <c r="G154" s="14"/>
-    </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F154" s="13"/>
+      <c r="G154" s="13"/>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A155" s="2"/>
       <c r="B155" s="3"/>
       <c r="C155" s="3"/>
-      <c r="D155" s="14"/>
+      <c r="D155" s="13"/>
       <c r="E155" s="12"/>
-      <c r="F155" s="14"/>
-      <c r="G155" s="14"/>
-    </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F155" s="13"/>
+      <c r="G155" s="13"/>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A156" s="2"/>
       <c r="B156" s="3"/>
       <c r="C156" s="3"/>
-      <c r="D156" s="14"/>
+      <c r="D156" s="13"/>
       <c r="E156" s="12"/>
-      <c r="F156" s="14"/>
-      <c r="G156" s="14"/>
-    </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F156" s="13"/>
+      <c r="G156" s="13"/>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A157" s="2"/>
       <c r="B157" s="3"/>
       <c r="C157" s="3"/>
-      <c r="D157" s="14"/>
+      <c r="D157" s="13"/>
       <c r="E157" s="12"/>
-      <c r="F157" s="14"/>
-      <c r="G157" s="14"/>
-    </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F157" s="13"/>
+      <c r="G157" s="13"/>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A158" s="2"/>
       <c r="B158" s="3"/>
       <c r="C158" s="3"/>
-      <c r="D158" s="14"/>
+      <c r="D158" s="13"/>
       <c r="E158" s="12"/>
-      <c r="F158" s="14"/>
-      <c r="G158" s="14"/>
-    </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F158" s="13"/>
+      <c r="G158" s="13"/>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A159" s="2"/>
       <c r="B159" s="3"/>
       <c r="C159" s="3"/>
-      <c r="D159" s="14"/>
+      <c r="D159" s="13"/>
       <c r="E159" s="12"/>
-      <c r="F159" s="14"/>
-      <c r="G159" s="14"/>
-    </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F159" s="13"/>
+      <c r="G159" s="13"/>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A160" s="2"/>
       <c r="B160" s="3"/>
       <c r="C160" s="3"/>
-      <c r="D160" s="14"/>
+      <c r="D160" s="13"/>
       <c r="E160" s="12"/>
-      <c r="F160" s="14"/>
-      <c r="G160" s="14"/>
-    </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F160" s="13"/>
+      <c r="G160" s="13"/>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A161" s="2"/>
       <c r="B161" s="3"/>
       <c r="C161" s="3"/>
-      <c r="D161" s="14"/>
+      <c r="D161" s="13"/>
       <c r="E161" s="12"/>
-      <c r="F161" s="14"/>
-      <c r="G161" s="14"/>
-    </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F161" s="13"/>
+      <c r="G161" s="13"/>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A162" s="2"/>
       <c r="B162" s="3"/>
       <c r="C162" s="3"/>
-      <c r="D162" s="14"/>
+      <c r="D162" s="13"/>
       <c r="E162" s="12"/>
-      <c r="F162" s="14"/>
-      <c r="G162" s="14"/>
-    </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F162" s="13"/>
+      <c r="G162" s="13"/>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A163" s="2"/>
       <c r="B163" s="3"/>
       <c r="C163" s="3"/>
-      <c r="D163" s="14"/>
+      <c r="D163" s="13"/>
       <c r="E163" s="12"/>
-      <c r="F163" s="14"/>
-      <c r="G163" s="14"/>
-    </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F163" s="13"/>
+      <c r="G163" s="13"/>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A164" s="2"/>
       <c r="B164" s="3"/>
       <c r="C164" s="3"/>
-      <c r="D164" s="14"/>
+      <c r="D164" s="13"/>
       <c r="E164" s="12"/>
-      <c r="F164" s="14"/>
-      <c r="G164" s="14"/>
-    </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F164" s="13"/>
+      <c r="G164" s="13"/>
+    </row>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A165" s="2"/>
       <c r="B165" s="3"/>
       <c r="C165" s="3"/>
-      <c r="D165" s="14"/>
+      <c r="D165" s="13"/>
       <c r="E165" s="12"/>
-      <c r="F165" s="14"/>
-      <c r="G165" s="14"/>
-    </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F165" s="13"/>
+      <c r="G165" s="13"/>
+    </row>
+    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A166" s="2"/>
       <c r="B166" s="3"/>
       <c r="C166" s="3"/>
-      <c r="D166" s="14"/>
+      <c r="D166" s="13"/>
       <c r="E166" s="12"/>
-      <c r="F166" s="14"/>
-      <c r="G166" s="14"/>
-    </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F166" s="13"/>
+      <c r="G166" s="13"/>
+    </row>
+    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A167" s="2"/>
       <c r="B167" s="3"/>
       <c r="C167" s="3"/>
-      <c r="D167" s="14"/>
+      <c r="D167" s="13"/>
       <c r="E167" s="12"/>
-      <c r="F167" s="14"/>
-      <c r="G167" s="14"/>
-    </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F167" s="13"/>
+      <c r="G167" s="13"/>
+    </row>
+    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A168" s="2"/>
       <c r="B168" s="3"/>
       <c r="C168" s="3"/>
-      <c r="D168" s="14"/>
+      <c r="D168" s="13"/>
       <c r="E168" s="12"/>
-      <c r="F168" s="14"/>
-      <c r="G168" s="14"/>
-    </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F168" s="13"/>
+      <c r="G168" s="13"/>
+    </row>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A169" s="2"/>
       <c r="B169" s="3"/>
       <c r="C169" s="3"/>
-      <c r="D169" s="14"/>
+      <c r="D169" s="13"/>
       <c r="E169" s="12"/>
-      <c r="F169" s="14"/>
-      <c r="G169" s="14"/>
-    </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F169" s="13"/>
+      <c r="G169" s="13"/>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A170" s="2"/>
       <c r="B170" s="3"/>
       <c r="C170" s="3"/>
-      <c r="D170" s="14"/>
+      <c r="D170" s="13"/>
       <c r="E170" s="12"/>
-      <c r="F170" s="14"/>
-      <c r="G170" s="14"/>
-    </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F170" s="13"/>
+      <c r="G170" s="13"/>
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A171" s="2"/>
       <c r="B171" s="3"/>
       <c r="C171" s="3"/>
-      <c r="D171" s="14"/>
+      <c r="D171" s="13"/>
       <c r="E171" s="12"/>
-      <c r="F171" s="14"/>
-      <c r="G171" s="14"/>
-    </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F171" s="13"/>
+      <c r="G171" s="13"/>
+    </row>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A172" s="2"/>
       <c r="B172" s="3"/>
       <c r="C172" s="3"/>
-      <c r="D172" s="14"/>
+      <c r="D172" s="13"/>
       <c r="E172" s="12"/>
-      <c r="F172" s="14"/>
-      <c r="G172" s="14"/>
-    </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F172" s="13"/>
+      <c r="G172" s="13"/>
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A173" s="2"/>
       <c r="B173" s="3"/>
       <c r="C173" s="3"/>
-      <c r="D173" s="14"/>
+      <c r="D173" s="13"/>
       <c r="E173" s="12"/>
-      <c r="F173" s="14"/>
-      <c r="G173" s="14"/>
-    </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F173" s="13"/>
+      <c r="G173" s="13"/>
+    </row>
+    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A174" s="2"/>
       <c r="B174" s="3"/>
       <c r="C174" s="3"/>
-      <c r="D174" s="14"/>
+      <c r="D174" s="13"/>
       <c r="E174" s="12"/>
-      <c r="F174" s="14"/>
-      <c r="G174" s="14"/>
-    </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F174" s="13"/>
+      <c r="G174" s="13"/>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A175" s="2"/>
       <c r="B175" s="3"/>
       <c r="C175" s="3"/>
-      <c r="D175" s="14"/>
+      <c r="D175" s="13"/>
       <c r="E175" s="12"/>
-      <c r="F175" s="14"/>
-      <c r="G175" s="14"/>
-    </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F175" s="13"/>
+      <c r="G175" s="13"/>
+    </row>
+    <row r="176" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A176" s="2"/>
       <c r="B176" s="3"/>
       <c r="C176" s="3"/>
-      <c r="D176" s="14"/>
+      <c r="D176" s="13"/>
       <c r="E176" s="12"/>
-      <c r="F176" s="14"/>
-      <c r="G176" s="14"/>
-    </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F176" s="13"/>
+      <c r="G176" s="13"/>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A177" s="2"/>
       <c r="B177" s="3"/>
       <c r="C177" s="3"/>
-      <c r="D177" s="14"/>
+      <c r="D177" s="13"/>
       <c r="E177" s="12"/>
-      <c r="F177" s="14"/>
-      <c r="G177" s="14"/>
-    </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F177" s="13"/>
+      <c r="G177" s="13"/>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A178" s="2"/>
       <c r="B178" s="3"/>
       <c r="C178" s="3"/>
-      <c r="D178" s="14"/>
+      <c r="D178" s="13"/>
       <c r="E178" s="12"/>
-      <c r="F178" s="14"/>
-      <c r="G178" s="14"/>
-    </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F178" s="13"/>
+      <c r="G178" s="13"/>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A179" s="2"/>
       <c r="B179" s="3"/>
       <c r="C179" s="3"/>
-      <c r="D179" s="14"/>
+      <c r="D179" s="13"/>
       <c r="E179" s="12"/>
-      <c r="F179" s="14"/>
-      <c r="G179" s="14"/>
-    </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F179" s="13"/>
+      <c r="G179" s="13"/>
+    </row>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A180" s="2"/>
       <c r="B180" s="3"/>
       <c r="C180" s="3"/>
-      <c r="D180" s="14"/>
+      <c r="D180" s="13"/>
       <c r="E180" s="12"/>
-      <c r="F180" s="14"/>
-      <c r="G180" s="14"/>
-    </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F180" s="13"/>
+      <c r="G180" s="13"/>
+    </row>
+    <row r="181" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A181" s="2"/>
       <c r="B181" s="3"/>
       <c r="C181" s="3"/>
-      <c r="D181" s="14"/>
+      <c r="D181" s="13"/>
       <c r="E181" s="12"/>
-      <c r="F181" s="14"/>
-      <c r="G181" s="14"/>
-    </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F181" s="13"/>
+      <c r="G181" s="13"/>
+    </row>
+    <row r="182" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A182" s="2"/>
       <c r="B182" s="3"/>
       <c r="C182" s="3"/>
-      <c r="D182" s="14"/>
+      <c r="D182" s="13"/>
       <c r="E182" s="12"/>
-      <c r="F182" s="14"/>
-      <c r="G182" s="14"/>
-    </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F182" s="13"/>
+      <c r="G182" s="13"/>
+    </row>
+    <row r="183" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A183" s="2"/>
       <c r="B183" s="3"/>
       <c r="C183" s="3"/>
-      <c r="D183" s="14"/>
+      <c r="D183" s="13"/>
       <c r="E183" s="12"/>
-      <c r="F183" s="14"/>
-      <c r="G183" s="14"/>
-    </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F183" s="13"/>
+      <c r="G183" s="13"/>
+    </row>
+    <row r="184" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A184" s="2"/>
       <c r="B184" s="3"/>
       <c r="C184" s="3"/>
-      <c r="D184" s="14"/>
+      <c r="D184" s="13"/>
       <c r="E184" s="12"/>
-      <c r="F184" s="14"/>
-      <c r="G184" s="14"/>
-    </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F184" s="13"/>
+      <c r="G184" s="13"/>
+    </row>
+    <row r="185" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A185" s="2"/>
       <c r="B185" s="3"/>
       <c r="C185" s="3"/>
-      <c r="D185" s="14"/>
+      <c r="D185" s="13"/>
       <c r="E185" s="12"/>
-      <c r="F185" s="14"/>
-      <c r="G185" s="14"/>
-    </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F185" s="13"/>
+      <c r="G185" s="13"/>
+    </row>
+    <row r="186" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A186" s="2"/>
       <c r="B186" s="3"/>
       <c r="C186" s="3"/>
-      <c r="D186" s="14"/>
+      <c r="D186" s="13"/>
       <c r="E186" s="12"/>
-      <c r="F186" s="14"/>
-      <c r="G186" s="14"/>
-    </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F186" s="13"/>
+      <c r="G186" s="13"/>
+    </row>
+    <row r="187" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A187" s="2"/>
       <c r="B187" s="3"/>
       <c r="C187" s="3"/>
-      <c r="D187" s="14"/>
+      <c r="D187" s="13"/>
       <c r="E187" s="12"/>
-      <c r="F187" s="14"/>
-      <c r="G187" s="14"/>
-    </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F187" s="13"/>
+      <c r="G187" s="13"/>
+    </row>
+    <row r="188" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A188" s="2"/>
       <c r="B188" s="3"/>
       <c r="C188" s="3"/>
-      <c r="D188" s="14"/>
+      <c r="D188" s="13"/>
       <c r="E188" s="12"/>
-      <c r="F188" s="14"/>
-      <c r="G188" s="14"/>
-    </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F188" s="13"/>
+      <c r="G188" s="13"/>
+    </row>
+    <row r="189" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A189" s="2"/>
       <c r="B189" s="3"/>
       <c r="C189" s="3"/>
-      <c r="D189" s="14"/>
+      <c r="D189" s="13"/>
       <c r="E189" s="12"/>
-      <c r="F189" s="14"/>
-      <c r="G189" s="14"/>
-    </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F189" s="13"/>
+      <c r="G189" s="13"/>
+    </row>
+    <row r="190" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A190" s="2"/>
       <c r="B190" s="3"/>
       <c r="C190" s="3"/>
-      <c r="D190" s="14"/>
+      <c r="D190" s="13"/>
       <c r="E190" s="12"/>
-      <c r="F190" s="14"/>
-      <c r="G190" s="14"/>
-    </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F190" s="13"/>
+      <c r="G190" s="13"/>
+    </row>
+    <row r="191" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A191" s="2"/>
       <c r="B191" s="3"/>
       <c r="C191" s="3"/>
-      <c r="D191" s="14"/>
+      <c r="D191" s="13"/>
       <c r="E191" s="12"/>
-      <c r="F191" s="14"/>
-      <c r="G191" s="14"/>
-    </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F191" s="13"/>
+      <c r="G191" s="13"/>
+    </row>
+    <row r="192" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A192" s="2"/>
       <c r="B192" s="3"/>
       <c r="C192" s="3"/>
-      <c r="D192" s="14"/>
+      <c r="D192" s="13"/>
       <c r="E192" s="12"/>
-      <c r="F192" s="14"/>
-      <c r="G192" s="14"/>
-    </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F192" s="13"/>
+      <c r="G192" s="13"/>
+    </row>
+    <row r="193" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A193" s="2"/>
       <c r="B193" s="3"/>
       <c r="C193" s="3"/>
-      <c r="D193" s="14"/>
+      <c r="D193" s="13"/>
       <c r="E193" s="12"/>
-      <c r="F193" s="14"/>
-      <c r="G193" s="14"/>
-    </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F193" s="13"/>
+      <c r="G193" s="13"/>
+    </row>
+    <row r="194" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A194" s="2"/>
       <c r="B194" s="3"/>
       <c r="C194" s="3"/>
-      <c r="D194" s="14"/>
+      <c r="D194" s="13"/>
       <c r="E194" s="12"/>
-      <c r="F194" s="14"/>
-      <c r="G194" s="14"/>
-    </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F194" s="13"/>
+      <c r="G194" s="13"/>
+    </row>
+    <row r="195" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A195" s="2"/>
       <c r="B195" s="3"/>
       <c r="C195" s="3"/>
-      <c r="D195" s="14"/>
+      <c r="D195" s="13"/>
       <c r="E195" s="12"/>
-      <c r="F195" s="14"/>
-      <c r="G195" s="14"/>
-    </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F195" s="13"/>
+      <c r="G195" s="13"/>
+    </row>
+    <row r="196" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A196" s="2"/>
       <c r="B196" s="3"/>
       <c r="C196" s="3"/>
-      <c r="D196" s="14"/>
+      <c r="D196" s="13"/>
       <c r="E196" s="12"/>
-      <c r="F196" s="14"/>
-      <c r="G196" s="14"/>
-    </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F196" s="13"/>
+      <c r="G196" s="13"/>
+    </row>
+    <row r="197" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A197" s="2"/>
       <c r="B197" s="3"/>
       <c r="C197" s="3"/>
-      <c r="D197" s="14"/>
+      <c r="D197" s="13"/>
       <c r="E197" s="12"/>
-      <c r="F197" s="14"/>
-      <c r="G197" s="14"/>
-    </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F197" s="13"/>
+      <c r="G197" s="13"/>
+    </row>
+    <row r="198" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A198" s="2"/>
       <c r="B198" s="3"/>
       <c r="C198" s="3"/>
-      <c r="D198" s="14"/>
+      <c r="D198" s="13"/>
       <c r="E198" s="12"/>
-      <c r="F198" s="14"/>
-      <c r="G198" s="14"/>
-    </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F198" s="13"/>
+      <c r="G198" s="13"/>
+    </row>
+    <row r="199" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A199" s="2"/>
       <c r="B199" s="3"/>
       <c r="C199" s="3"/>
-      <c r="D199" s="14"/>
+      <c r="D199" s="13"/>
       <c r="E199" s="12"/>
-      <c r="F199" s="14"/>
-      <c r="G199" s="14"/>
-    </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F199" s="13"/>
+      <c r="G199" s="13"/>
+    </row>
+    <row r="200" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A200" s="2"/>
       <c r="B200" s="3"/>
       <c r="C200" s="3"/>
-      <c r="D200" s="14"/>
+      <c r="D200" s="13"/>
       <c r="E200" s="12"/>
-      <c r="F200" s="14"/>
-      <c r="G200" s="14"/>
-    </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F200" s="13"/>
+      <c r="G200" s="13"/>
+    </row>
+    <row r="201" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A201" s="2"/>
       <c r="B201" s="3"/>
       <c r="C201" s="3"/>
-      <c r="D201" s="14"/>
+      <c r="D201" s="13"/>
       <c r="E201" s="12"/>
-      <c r="F201" s="14"/>
-      <c r="G201" s="14"/>
-    </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F201" s="13"/>
+      <c r="G201" s="13"/>
+    </row>
+    <row r="202" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A202" s="2"/>
       <c r="B202" s="3"/>
       <c r="C202" s="3"/>
-      <c r="D202" s="14"/>
+      <c r="D202" s="13"/>
       <c r="E202" s="12"/>
-      <c r="F202" s="14"/>
-      <c r="G202" s="14"/>
-    </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F202" s="13"/>
+      <c r="G202" s="13"/>
+    </row>
+    <row r="203" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A203" s="2"/>
       <c r="B203" s="3"/>
       <c r="C203" s="3"/>
-      <c r="D203" s="14"/>
+      <c r="D203" s="13"/>
       <c r="E203" s="12"/>
-      <c r="F203" s="14"/>
-      <c r="G203" s="14"/>
-    </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F203" s="13"/>
+      <c r="G203" s="13"/>
+    </row>
+    <row r="204" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A204" s="2"/>
       <c r="B204" s="3"/>
       <c r="C204" s="3"/>
-      <c r="D204" s="14"/>
+      <c r="D204" s="13"/>
       <c r="E204" s="12"/>
-      <c r="F204" s="14"/>
-      <c r="G204" s="14"/>
-    </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F204" s="13"/>
+      <c r="G204" s="13"/>
+    </row>
+    <row r="205" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A205" s="2"/>
       <c r="B205" s="3"/>
       <c r="C205" s="3"/>
-      <c r="D205" s="14"/>
+      <c r="D205" s="13"/>
       <c r="E205" s="12"/>
-      <c r="F205" s="14"/>
-      <c r="G205" s="14"/>
-    </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F205" s="13"/>
+      <c r="G205" s="13"/>
+    </row>
+    <row r="206" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A206" s="2"/>
       <c r="B206" s="3"/>
       <c r="C206" s="3"/>
-      <c r="D206" s="14"/>
+      <c r="D206" s="13"/>
       <c r="E206" s="12"/>
-      <c r="F206" s="14"/>
-      <c r="G206" s="14"/>
-    </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F206" s="13"/>
+      <c r="G206" s="13"/>
+    </row>
+    <row r="207" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A207" s="2"/>
       <c r="B207" s="3"/>
       <c r="C207" s="3"/>
-      <c r="D207" s="14"/>
+      <c r="D207" s="13"/>
       <c r="E207" s="12"/>
-      <c r="F207" s="14"/>
-      <c r="G207" s="14"/>
-    </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F207" s="13"/>
+      <c r="G207" s="13"/>
+    </row>
+    <row r="208" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A208" s="2"/>
       <c r="B208" s="3"/>
       <c r="C208" s="3"/>
-      <c r="D208" s="14"/>
+      <c r="D208" s="13"/>
       <c r="E208" s="12"/>
-      <c r="F208" s="14"/>
-      <c r="G208" s="14"/>
-    </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F208" s="13"/>
+      <c r="G208" s="13"/>
+    </row>
+    <row r="209" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A209" s="2"/>
       <c r="B209" s="3"/>
       <c r="C209" s="3"/>
-      <c r="D209" s="14"/>
+      <c r="D209" s="13"/>
       <c r="E209" s="12"/>
-      <c r="F209" s="14"/>
-      <c r="G209" s="14"/>
-    </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F209" s="13"/>
+      <c r="G209" s="13"/>
+    </row>
+    <row r="210" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A210" s="2"/>
       <c r="B210" s="3"/>
       <c r="C210" s="3"/>
-      <c r="D210" s="14"/>
+      <c r="D210" s="13"/>
       <c r="E210" s="12"/>
-      <c r="F210" s="14"/>
-      <c r="G210" s="14"/>
-    </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F210" s="13"/>
+      <c r="G210" s="13"/>
+    </row>
+    <row r="211" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A211" s="2"/>
       <c r="B211" s="3"/>
       <c r="C211" s="3"/>
-      <c r="D211" s="14"/>
+      <c r="D211" s="13"/>
       <c r="E211" s="12"/>
-      <c r="F211" s="14"/>
-      <c r="G211" s="14"/>
-    </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F211" s="13"/>
+      <c r="G211" s="13"/>
+    </row>
+    <row r="212" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A212" s="2"/>
       <c r="B212" s="3"/>
       <c r="C212" s="3"/>
-      <c r="D212" s="14"/>
+      <c r="D212" s="13"/>
       <c r="E212" s="12"/>
-      <c r="F212" s="14"/>
-      <c r="G212" s="14"/>
-    </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F212" s="13"/>
+      <c r="G212" s="13"/>
+    </row>
+    <row r="213" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A213" s="2"/>
       <c r="B213" s="3"/>
       <c r="C213" s="3"/>
-      <c r="D213" s="14"/>
+      <c r="D213" s="13"/>
       <c r="E213" s="12"/>
-      <c r="F213" s="14"/>
-      <c r="G213" s="14"/>
-    </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F213" s="13"/>
+      <c r="G213" s="13"/>
+    </row>
+    <row r="214" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A214" s="2"/>
       <c r="B214" s="3"/>
       <c r="C214" s="3"/>
-      <c r="D214" s="14"/>
+      <c r="D214" s="13"/>
       <c r="E214" s="12"/>
-      <c r="F214" s="14"/>
-      <c r="G214" s="14"/>
-    </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F214" s="13"/>
+      <c r="G214" s="13"/>
+    </row>
+    <row r="215" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A215" s="2"/>
       <c r="B215" s="3"/>
       <c r="C215" s="3"/>
-      <c r="D215" s="14"/>
+      <c r="D215" s="13"/>
       <c r="E215" s="12"/>
-      <c r="F215" s="14"/>
-      <c r="G215" s="14"/>
-    </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F215" s="13"/>
+      <c r="G215" s="13"/>
+    </row>
+    <row r="216" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A216" s="2"/>
       <c r="B216" s="3"/>
       <c r="C216" s="3"/>
-      <c r="D216" s="14"/>
+      <c r="D216" s="13"/>
       <c r="E216" s="12"/>
-      <c r="F216" s="14"/>
-      <c r="G216" s="14"/>
-    </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F216" s="13"/>
+      <c r="G216" s="13"/>
+    </row>
+    <row r="217" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A217" s="2"/>
       <c r="B217" s="3"/>
       <c r="C217" s="3"/>
-      <c r="D217" s="14"/>
+      <c r="D217" s="13"/>
       <c r="E217" s="12"/>
-      <c r="F217" s="14"/>
-      <c r="G217" s="14"/>
-    </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F217" s="13"/>
+      <c r="G217" s="13"/>
+    </row>
+    <row r="218" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A218" s="2"/>
       <c r="B218" s="3"/>
       <c r="C218" s="3"/>
-      <c r="D218" s="14"/>
+      <c r="D218" s="13"/>
       <c r="E218" s="12"/>
-      <c r="F218" s="14"/>
-      <c r="G218" s="14"/>
-    </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F218" s="13"/>
+      <c r="G218" s="13"/>
+    </row>
+    <row r="219" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A219" s="2"/>
       <c r="B219" s="3"/>
       <c r="C219" s="3"/>
-      <c r="D219" s="14"/>
+      <c r="D219" s="13"/>
       <c r="E219" s="12"/>
-      <c r="F219" s="14"/>
-      <c r="G219" s="14"/>
-    </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F219" s="13"/>
+      <c r="G219" s="13"/>
+    </row>
+    <row r="220" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A220" s="2"/>
       <c r="B220" s="3"/>
       <c r="C220" s="3"/>
-      <c r="D220" s="14"/>
+      <c r="D220" s="13"/>
       <c r="E220" s="12"/>
-      <c r="F220" s="14"/>
-      <c r="G220" s="14"/>
-    </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F220" s="13"/>
+      <c r="G220" s="13"/>
+    </row>
+    <row r="221" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A221" s="2"/>
       <c r="B221" s="3"/>
       <c r="C221" s="3"/>
-      <c r="D221" s="14"/>
+      <c r="D221" s="13"/>
       <c r="E221" s="12"/>
-      <c r="F221" s="14"/>
-      <c r="G221" s="14"/>
-    </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F221" s="13"/>
+      <c r="G221" s="13"/>
+    </row>
+    <row r="222" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A222" s="2"/>
       <c r="B222" s="3"/>
       <c r="C222" s="3"/>
-      <c r="D222" s="14"/>
+      <c r="D222" s="13"/>
       <c r="E222" s="12"/>
-      <c r="F222" s="14"/>
-      <c r="G222" s="14"/>
-    </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F222" s="13"/>
+      <c r="G222" s="13"/>
+    </row>
+    <row r="223" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A223" s="2"/>
       <c r="B223" s="3"/>
       <c r="C223" s="3"/>
-      <c r="D223" s="14"/>
+      <c r="D223" s="13"/>
       <c r="E223" s="12"/>
-      <c r="F223" s="14"/>
-      <c r="G223" s="14"/>
-    </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F223" s="13"/>
+      <c r="G223" s="13"/>
+    </row>
+    <row r="224" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A224" s="2"/>
       <c r="B224" s="3"/>
       <c r="C224" s="3"/>
-      <c r="D224" s="14"/>
+      <c r="D224" s="13"/>
       <c r="E224" s="12"/>
-      <c r="F224" s="14"/>
-      <c r="G224" s="14"/>
-    </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F224" s="13"/>
+      <c r="G224" s="13"/>
+    </row>
+    <row r="225" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A225" s="2"/>
       <c r="B225" s="3"/>
       <c r="C225" s="3"/>
-      <c r="D225" s="14"/>
+      <c r="D225" s="13"/>
       <c r="E225" s="12"/>
-      <c r="F225" s="14"/>
-      <c r="G225" s="14"/>
-    </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F225" s="13"/>
+      <c r="G225" s="13"/>
+    </row>
+    <row r="226" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A226" s="2"/>
       <c r="B226" s="3"/>
       <c r="C226" s="3"/>
-      <c r="D226" s="14"/>
+      <c r="D226" s="13"/>
       <c r="E226" s="12"/>
-      <c r="F226" s="14"/>
-      <c r="G226" s="14"/>
-    </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F226" s="13"/>
+      <c r="G226" s="13"/>
+    </row>
+    <row r="227" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A227" s="2"/>
       <c r="B227" s="3"/>
       <c r="C227" s="3"/>
-      <c r="D227" s="14"/>
+      <c r="D227" s="13"/>
       <c r="E227" s="12"/>
-      <c r="F227" s="14"/>
-      <c r="G227" s="14"/>
-    </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F227" s="13"/>
+      <c r="G227" s="13"/>
+    </row>
+    <row r="228" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A228" s="2"/>
       <c r="B228" s="3"/>
       <c r="C228" s="3"/>
-      <c r="D228" s="14"/>
+      <c r="D228" s="13"/>
       <c r="E228" s="12"/>
-      <c r="F228" s="14"/>
-      <c r="G228" s="14"/>
-    </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F228" s="13"/>
+      <c r="G228" s="13"/>
+    </row>
+    <row r="229" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A229" s="2"/>
       <c r="B229" s="3"/>
       <c r="C229" s="3"/>
-      <c r="D229" s="14"/>
+      <c r="D229" s="13"/>
       <c r="E229" s="12"/>
-      <c r="F229" s="14"/>
-      <c r="G229" s="14"/>
-    </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F229" s="13"/>
+      <c r="G229" s="13"/>
+    </row>
+    <row r="230" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A230" s="2"/>
       <c r="B230" s="3"/>
       <c r="C230" s="3"/>
-      <c r="D230" s="14"/>
+      <c r="D230" s="13"/>
       <c r="E230" s="12"/>
-      <c r="F230" s="14"/>
-      <c r="G230" s="14"/>
-    </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F230" s="13"/>
+      <c r="G230" s="13"/>
+    </row>
+    <row r="231" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A231" s="2"/>
       <c r="B231" s="3"/>
       <c r="C231" s="3"/>
-      <c r="D231" s="14"/>
+      <c r="D231" s="13"/>
       <c r="E231" s="12"/>
-      <c r="F231" s="14"/>
-      <c r="G231" s="14"/>
-    </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F231" s="13"/>
+      <c r="G231" s="13"/>
+    </row>
+    <row r="232" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A232" s="2"/>
       <c r="B232" s="3"/>
       <c r="C232" s="3"/>
-      <c r="D232" s="14"/>
+      <c r="D232" s="13"/>
       <c r="E232" s="12"/>
-      <c r="F232" s="14"/>
-      <c r="G232" s="14"/>
-    </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F232" s="13"/>
+      <c r="G232" s="13"/>
+    </row>
+    <row r="233" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A233" s="2"/>
       <c r="B233" s="3"/>
       <c r="C233" s="3"/>
-      <c r="D233" s="14"/>
+      <c r="D233" s="13"/>
       <c r="E233" s="12"/>
-      <c r="F233" s="14"/>
-      <c r="G233" s="14"/>
-    </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F233" s="13"/>
+      <c r="G233" s="13"/>
+    </row>
+    <row r="234" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A234" s="2"/>
       <c r="B234" s="3"/>
       <c r="C234" s="3"/>
-      <c r="D234" s="14"/>
+      <c r="D234" s="13"/>
       <c r="E234" s="12"/>
-      <c r="F234" s="14"/>
-      <c r="G234" s="14"/>
-    </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F234" s="13"/>
+      <c r="G234" s="13"/>
+    </row>
+    <row r="235" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A235" s="2"/>
       <c r="B235" s="3"/>
       <c r="C235" s="3"/>
-      <c r="D235" s="14"/>
+      <c r="D235" s="13"/>
       <c r="E235" s="12"/>
-      <c r="F235" s="14"/>
-      <c r="G235" s="14"/>
-    </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F235" s="13"/>
+      <c r="G235" s="13"/>
+    </row>
+    <row r="236" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A236" s="2"/>
       <c r="B236" s="3"/>
       <c r="C236" s="3"/>
-      <c r="D236" s="14"/>
+      <c r="D236" s="13"/>
       <c r="E236" s="12"/>
-      <c r="F236" s="14"/>
-      <c r="G236" s="14"/>
-    </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F236" s="13"/>
+      <c r="G236" s="13"/>
+    </row>
+    <row r="237" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A237" s="2"/>
       <c r="B237" s="3"/>
       <c r="C237" s="3"/>
-      <c r="D237" s="14"/>
+      <c r="D237" s="13"/>
       <c r="E237" s="12"/>
-      <c r="F237" s="14"/>
-      <c r="G237" s="14"/>
-    </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F237" s="13"/>
+      <c r="G237" s="13"/>
+    </row>
+    <row r="238" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A238" s="2"/>
       <c r="B238" s="3"/>
       <c r="C238" s="3"/>
-      <c r="D238" s="14"/>
+      <c r="D238" s="13"/>
       <c r="E238" s="12"/>
-      <c r="F238" s="14"/>
-      <c r="G238" s="14"/>
-    </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F238" s="13"/>
+      <c r="G238" s="13"/>
+    </row>
+    <row r="239" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A239" s="2"/>
       <c r="B239" s="3"/>
       <c r="C239" s="3"/>
-      <c r="D239" s="14"/>
+      <c r="D239" s="13"/>
       <c r="E239" s="12"/>
-      <c r="F239" s="14"/>
-      <c r="G239" s="14"/>
-    </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F239" s="13"/>
+      <c r="G239" s="13"/>
+    </row>
+    <row r="240" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A240" s="2"/>
       <c r="B240" s="3"/>
       <c r="C240" s="3"/>
-      <c r="D240" s="14"/>
+      <c r="D240" s="13"/>
       <c r="E240" s="12"/>
-      <c r="F240" s="14"/>
-      <c r="G240" s="14"/>
-    </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F240" s="13"/>
+      <c r="G240" s="13"/>
+    </row>
+    <row r="241" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A241" s="2"/>
       <c r="B241" s="3"/>
       <c r="C241" s="3"/>
-      <c r="D241" s="14"/>
+      <c r="D241" s="13"/>
       <c r="E241" s="12"/>
-      <c r="F241" s="14"/>
-      <c r="G241" s="14"/>
-    </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F241" s="13"/>
+      <c r="G241" s="13"/>
+    </row>
+    <row r="242" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A242" s="2"/>
       <c r="B242" s="3"/>
       <c r="C242" s="3"/>
-      <c r="D242" s="14"/>
+      <c r="D242" s="13"/>
       <c r="E242" s="12"/>
-      <c r="F242" s="14"/>
-      <c r="G242" s="14"/>
-    </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F242" s="13"/>
+      <c r="G242" s="13"/>
+    </row>
+    <row r="243" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A243" s="2"/>
       <c r="B243" s="3"/>
       <c r="C243" s="3"/>
-      <c r="D243" s="14"/>
+      <c r="D243" s="13"/>
       <c r="E243" s="12"/>
-      <c r="F243" s="14"/>
-      <c r="G243" s="14"/>
-    </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F243" s="13"/>
+      <c r="G243" s="13"/>
+    </row>
+    <row r="244" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A244" s="2"/>
       <c r="B244" s="3"/>
       <c r="C244" s="3"/>
-      <c r="D244" s="14"/>
+      <c r="D244" s="13"/>
       <c r="E244" s="12"/>
-      <c r="F244" s="14"/>
-      <c r="G244" s="14"/>
-    </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F244" s="13"/>
+      <c r="G244" s="13"/>
+    </row>
+    <row r="245" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A245" s="2"/>
       <c r="B245" s="3"/>
       <c r="C245" s="3"/>
-      <c r="D245" s="14"/>
+      <c r="D245" s="13"/>
       <c r="E245" s="12"/>
-      <c r="F245" s="14"/>
-      <c r="G245" s="14"/>
-    </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F245" s="13"/>
+      <c r="G245" s="13"/>
+    </row>
+    <row r="246" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A246" s="2"/>
       <c r="B246" s="3"/>
       <c r="C246" s="3"/>
-      <c r="D246" s="14"/>
+      <c r="D246" s="13"/>
       <c r="E246" s="12"/>
-      <c r="F246" s="14"/>
-      <c r="G246" s="14"/>
-    </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F246" s="13"/>
+      <c r="G246" s="13"/>
+    </row>
+    <row r="247" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A247" s="2"/>
       <c r="B247" s="3"/>
       <c r="C247" s="3"/>
-      <c r="D247" s="14"/>
+      <c r="D247" s="13"/>
       <c r="E247" s="12"/>
-      <c r="F247" s="14"/>
-      <c r="G247" s="14"/>
-    </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F247" s="13"/>
+      <c r="G247" s="13"/>
+    </row>
+    <row r="248" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A248" s="2"/>
       <c r="B248" s="3"/>
       <c r="C248" s="3"/>
-      <c r="D248" s="14"/>
+      <c r="D248" s="13"/>
       <c r="E248" s="12"/>
-      <c r="F248" s="14"/>
-      <c r="G248" s="14"/>
-    </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F248" s="13"/>
+      <c r="G248" s="13"/>
+    </row>
+    <row r="249" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A249" s="2"/>
       <c r="B249" s="3"/>
       <c r="C249" s="3"/>
-      <c r="D249" s="14"/>
+      <c r="D249" s="13"/>
       <c r="E249" s="12"/>
-      <c r="F249" s="14"/>
-      <c r="G249" s="14"/>
-    </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F249" s="13"/>
+      <c r="G249" s="13"/>
+    </row>
+    <row r="250" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A250" s="2"/>
       <c r="B250" s="3"/>
       <c r="C250" s="3"/>
-      <c r="D250" s="14"/>
+      <c r="D250" s="13"/>
       <c r="E250" s="12"/>
-      <c r="F250" s="14"/>
-      <c r="G250" s="14"/>
-    </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F250" s="13"/>
+      <c r="G250" s="13"/>
+    </row>
+    <row r="251" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A251" s="2"/>
       <c r="B251" s="3"/>
       <c r="C251" s="3"/>
-      <c r="D251" s="14"/>
+      <c r="D251" s="13"/>
       <c r="E251" s="12"/>
-      <c r="F251" s="14"/>
-      <c r="G251" s="14"/>
-    </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F251" s="13"/>
+      <c r="G251" s="13"/>
+    </row>
+    <row r="252" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A252" s="2"/>
       <c r="B252" s="3"/>
       <c r="C252" s="3"/>
-      <c r="D252" s="14"/>
+      <c r="D252" s="13"/>
       <c r="E252" s="12"/>
-      <c r="F252" s="14"/>
-      <c r="G252" s="14"/>
-    </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F252" s="13"/>
+      <c r="G252" s="13"/>
+    </row>
+    <row r="253" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A253" s="2"/>
       <c r="B253" s="3"/>
       <c r="C253" s="3"/>
-      <c r="D253" s="14"/>
+      <c r="D253" s="13"/>
       <c r="E253" s="12"/>
-      <c r="F253" s="14"/>
-      <c r="G253" s="14"/>
-    </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F253" s="13"/>
+      <c r="G253" s="13"/>
+    </row>
+    <row r="254" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A254" s="2"/>
       <c r="B254" s="3"/>
       <c r="C254" s="3"/>
-      <c r="D254" s="14"/>
+      <c r="D254" s="13"/>
       <c r="E254" s="12"/>
-      <c r="F254" s="14"/>
-      <c r="G254" s="14"/>
-    </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F254" s="13"/>
+      <c r="G254" s="13"/>
+    </row>
+    <row r="255" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A255" s="2"/>
       <c r="B255" s="3"/>
       <c r="C255" s="3"/>
-      <c r="D255" s="14"/>
+      <c r="D255" s="13"/>
       <c r="E255" s="12"/>
-      <c r="F255" s="14"/>
-      <c r="G255" s="14"/>
-    </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F255" s="13"/>
+      <c r="G255" s="13"/>
+    </row>
+    <row r="256" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A256" s="2"/>
       <c r="B256" s="3"/>
       <c r="C256" s="3"/>
-      <c r="D256" s="14"/>
+      <c r="D256" s="13"/>
       <c r="E256" s="12"/>
-      <c r="F256" s="14"/>
-      <c r="G256" s="14"/>
-    </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F256" s="13"/>
+      <c r="G256" s="13"/>
+    </row>
+    <row r="257" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A257" s="2"/>
       <c r="B257" s="3"/>
       <c r="C257" s="3"/>
-      <c r="D257" s="14"/>
+      <c r="D257" s="13"/>
       <c r="E257" s="12"/>
-      <c r="F257" s="14"/>
-      <c r="G257" s="14"/>
-    </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F257" s="13"/>
+      <c r="G257" s="13"/>
+    </row>
+    <row r="258" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A258" s="2"/>
       <c r="B258" s="3"/>
       <c r="C258" s="3"/>
-      <c r="D258" s="14"/>
+      <c r="D258" s="13"/>
       <c r="E258" s="12"/>
-      <c r="F258" s="14"/>
-      <c r="G258" s="14"/>
-    </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F258" s="13"/>
+      <c r="G258" s="13"/>
+    </row>
+    <row r="259" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A259" s="2"/>
       <c r="B259" s="3"/>
       <c r="C259" s="3"/>
-      <c r="D259" s="14"/>
+      <c r="D259" s="13"/>
       <c r="E259" s="12"/>
-      <c r="F259" s="14"/>
-      <c r="G259" s="14"/>
-    </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F259" s="13"/>
+      <c r="G259" s="13"/>
+    </row>
+    <row r="260" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A260" s="2"/>
       <c r="B260" s="3"/>
       <c r="C260" s="3"/>
-      <c r="D260" s="14"/>
+      <c r="D260" s="13"/>
       <c r="E260" s="12"/>
-      <c r="F260" s="14"/>
-      <c r="G260" s="14"/>
-    </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F260" s="13"/>
+      <c r="G260" s="13"/>
+    </row>
+    <row r="261" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A261" s="2"/>
       <c r="B261" s="3"/>
       <c r="C261" s="3"/>
-      <c r="D261" s="14"/>
+      <c r="D261" s="13"/>
       <c r="E261" s="12"/>
-      <c r="F261" s="14"/>
-      <c r="G261" s="14"/>
-    </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F261" s="13"/>
+      <c r="G261" s="13"/>
+    </row>
+    <row r="262" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A262" s="2"/>
       <c r="B262" s="3"/>
       <c r="C262" s="3"/>
-      <c r="D262" s="14"/>
+      <c r="D262" s="13"/>
       <c r="E262" s="12"/>
-      <c r="F262" s="14"/>
-      <c r="G262" s="14"/>
-    </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F262" s="13"/>
+      <c r="G262" s="13"/>
+    </row>
+    <row r="263" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A263" s="2"/>
       <c r="B263" s="3"/>
       <c r="C263" s="3"/>
-      <c r="D263" s="14"/>
+      <c r="D263" s="13"/>
       <c r="E263" s="12"/>
-      <c r="F263" s="14"/>
-      <c r="G263" s="14"/>
-    </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F263" s="13"/>
+      <c r="G263" s="13"/>
+    </row>
+    <row r="264" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A264" s="2"/>
       <c r="B264" s="3"/>
       <c r="C264" s="3"/>
-      <c r="D264" s="14"/>
+      <c r="D264" s="13"/>
       <c r="E264" s="12"/>
-      <c r="F264" s="14"/>
-      <c r="G264" s="14"/>
-    </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F264" s="13"/>
+      <c r="G264" s="13"/>
+    </row>
+    <row r="265" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A265" s="2"/>
       <c r="B265" s="3"/>
       <c r="C265" s="3"/>
-      <c r="D265" s="14"/>
+      <c r="D265" s="13"/>
       <c r="E265" s="12"/>
-      <c r="F265" s="14"/>
-      <c r="G265" s="14"/>
-    </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F265" s="13"/>
+      <c r="G265" s="13"/>
+    </row>
+    <row r="266" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A266" s="2"/>
       <c r="B266" s="3"/>
       <c r="C266" s="3"/>
-      <c r="D266" s="14"/>
+      <c r="D266" s="13"/>
       <c r="E266" s="12"/>
-      <c r="F266" s="14"/>
-      <c r="G266" s="14"/>
-    </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F266" s="13"/>
+      <c r="G266" s="13"/>
+    </row>
+    <row r="267" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A267" s="2"/>
       <c r="B267" s="3"/>
       <c r="C267" s="3"/>
-      <c r="D267" s="14"/>
+      <c r="D267" s="13"/>
       <c r="E267" s="12"/>
-      <c r="F267" s="14"/>
-      <c r="G267" s="14"/>
-    </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F267" s="13"/>
+      <c r="G267" s="13"/>
+    </row>
+    <row r="268" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A268" s="2"/>
       <c r="B268" s="3"/>
       <c r="C268" s="3"/>
-      <c r="D268" s="14"/>
+      <c r="D268" s="13"/>
       <c r="E268" s="12"/>
-      <c r="F268" s="14"/>
-      <c r="G268" s="14"/>
-    </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F268" s="13"/>
+      <c r="G268" s="13"/>
+    </row>
+    <row r="269" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A269" s="2"/>
-      <c r="D269" s="14"/>
+      <c r="D269" s="13"/>
       <c r="E269" s="12"/>
-      <c r="F269" s="14"/>
-      <c r="G269" s="14"/>
-    </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="D270" s="14"/>
+      <c r="F269" s="13"/>
+      <c r="G269" s="13"/>
+    </row>
+    <row r="270" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D270" s="13"/>
       <c r="E270" s="12"/>
-      <c r="F270" s="14"/>
-      <c r="G270" s="14"/>
-    </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="D271" s="14"/>
-      <c r="E271" s="14"/>
-      <c r="F271" s="14"/>
-      <c r="G271" s="14"/>
+      <c r="F270" s="13"/>
+      <c r="G270" s="13"/>
+    </row>
+    <row r="271" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D271" s="13"/>
+      <c r="E271" s="13"/>
+      <c r="F271" s="13"/>
+      <c r="G271" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -4378,17 +4382,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="100.7265625" customWidth="1"/>
+    <col min="1" max="1" width="100.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A1" s="20" t="s">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" s="19" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="48" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:1" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>16</v>
       </c>
